--- a/07_prisma/prisma_counts.xlsx
+++ b/07_prisma/prisma_counts.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="PRISMA Counts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRISMA_Counts" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,21 +27,14 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -56,10 +49,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -426,13 +422,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="38.7" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -448,190 +444,214 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>database_or_source</t>
+          <t>breakdown</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>source_file</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Records identified through database searching</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>TEMPLATE 000</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>EBSCOhost</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>TEMPLATE - total hits from search_history.xlsx</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Records identified from databases</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1815</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Xplore 45; ACM DL 134; SpringerLink 423; ScienceDirect 217; EBSCO HOST 996</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>01_search/search_history.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Additional records identified through other sources</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>TEMPLATE 000</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Snowballing/manual</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>TEMPLATE - if applicable</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Records identified via other methods</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Forward/backward citation tracking</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>01_search/search_history.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Records after duplicates removed</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>TEMPLATE 000</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>All sources</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>TEMPLATE</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Duplicate records removed</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>attribution of duplicates not reproducible - see docs/known_issues.md</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>01_search/search_history.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Records screened (title/abstract)</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>TEMPLATE 000</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>All sources</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>TEMPLATE</t>
-        </is>
-      </c>
+      <c r="B5" s="2" t="n">
+        <v>1599</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Records excluded (title/abstract)</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>TEMPLATE 000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>All sources</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>TEMPLATE - see exclusion_reasons.md</t>
-        </is>
-      </c>
+      <c r="B6" s="2" t="n">
+        <v>1583</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>topical irrelevance, publication type, scope, language (per-record log not archived)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Full-text articles assessed for eligibility</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>TEMPLATE 000</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>All sources</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>TEMPLATE</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Reports sought for retrieval</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Full-text articles excluded, with reasons</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>TEMPLATE 000</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>All sources</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>TEMPLATE - see exclusion_reasons.md</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Reports not retrieved</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Studies included in qualitative synthesis</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>TEMPLATE 000</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>All sources</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>TEMPLATE - matches 06_included_studies</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Reports assessed for eligibility</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>02_screening/screening.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Reports excluded (full text)</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>outside multi-cloud governance scope: 5; not peer-reviewed: 1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>02_screening/screening.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Studies included (Phase 1)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>8 database search + 2 citation tracking</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>06_included_studies/included_studies.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Normative sources (Phase 2, outside PRISMA)</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>ISO/IEC 27001:2022; NIST CSF 2.0; CSA Security Guidance v5; NIST SP 800-210</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>06_included_studies/included_studies.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Total corpus</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
